--- a/artfynd/A 52211-2025 artfynd.xlsx
+++ b/artfynd/A 52211-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>100155258</v>
       </c>
       <c r="B2" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>668363.971338694</v>
+        <v>668364</v>
       </c>
       <c r="R2" t="n">
-        <v>6700887.60417555</v>
+        <v>6700888</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -797,16 +792,11 @@
         <v>100213213</v>
       </c>
       <c r="B3" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -839,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668295.3603314518</v>
+        <v>668295</v>
       </c>
       <c r="R3" t="n">
-        <v>6700871.060178137</v>
+        <v>6700871</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,19 +862,9 @@
           <t>2022-04-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,6 +888,223 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100213152</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gubbsvedsmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>668356</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6700894</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>spelspillning</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100255047</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Forsmark, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>668364</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6700876</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hållnäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-04-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spelspillning i hög</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Linnéa Sigvardsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linnéa Sigvardsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52211-2025 artfynd.xlsx
+++ b/artfynd/A 52211-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100155258</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100213213</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100213152</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,8 +1125,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100255047</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>